--- a/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido</t>
+          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,75; 21,26</t>
+          <t>17,76; 21,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,32; 21,61</t>
+          <t>17,22; 21,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,11; 20,66</t>
+          <t>15,17; 21,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,2; 21,34</t>
+          <t>17,23; 21,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,8; 18,42</t>
+          <t>16,73; 18,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,12</t>
+          <t>15,83; 20,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,9; 20,61</t>
+          <t>17,82; 20,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 19,44</t>
+          <t>17,26; 19,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,77</t>
+          <t>15,95; 20,15</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 18,9</t>
+          <t>17,69; 18,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 17,92</t>
+          <t>16,94; 17,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 20,33</t>
+          <t>17,21; 20,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,26; 19,23</t>
+          <t>18,31; 19,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 18,26</t>
+          <t>17,2; 18,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,34; 18,78</t>
+          <t>17,39; 18,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 18,89</t>
+          <t>18,11; 18,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,92</t>
+          <t>17,21; 17,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,5; 19,15</t>
+          <t>17,5; 18,99</t>
         </is>
       </c>
     </row>
@@ -902,42 +902,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 19,05</t>
+          <t>18,31; 19,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,96; 19,36</t>
+          <t>17,94; 19,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,47; 20,7</t>
+          <t>19,4; 20,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,86; 19,82</t>
+          <t>18,87; 19,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 20,17</t>
+          <t>18,71; 20,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 20,41</t>
+          <t>19,57; 20,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 19,3</t>
+          <t>18,7; 19,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,54; 19,55</t>
+          <t>18,52; 19,6</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 21,48</t>
+          <t>20,57; 21,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 21,14</t>
+          <t>20,31; 21,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 22,22</t>
+          <t>19,84; 22,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,98; 21,84</t>
+          <t>20,97; 21,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 21,32</t>
+          <t>20,4; 21,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 21,55</t>
+          <t>20,04; 21,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,83; 21,5</t>
+          <t>20,89; 21,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,43; 21,11</t>
+          <t>20,47; 21,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,22; 21,66</t>
+          <t>20,14; 21,62</t>
         </is>
       </c>
     </row>
@@ -1117,32 +1117,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,19; 19,89</t>
+          <t>19,18; 19,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,07</t>
+          <t>18,5; 19,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,84; 20,67</t>
+          <t>18,79; 20,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,48; 20,09</t>
+          <t>19,45; 20,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,31</t>
+          <t>18,72; 19,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,06; 19,96</t>
+          <t>19,09; 19,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,08</t>
+          <t>18,68; 19,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,11; 20,09</t>
+          <t>19,08; 20,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores medido (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,76; 21,28</t>
+          <t>17,78; 21,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 21,45</t>
+          <t>17,34; 22,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 21,38</t>
+          <t>15,21; 21,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 21,22</t>
+          <t>17,13; 21,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,73; 18,35</t>
+          <t>16,69; 18,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 20,39</t>
+          <t>15,83; 20,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,42</t>
+          <t>17,86; 20,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,62</t>
+          <t>17,28; 19,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 20,15</t>
+          <t>15,68; 19,47</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,69; 18,91</t>
+          <t>17,7; 18,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,94; 17,91</t>
+          <t>16,91; 17,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 20,14</t>
+          <t>17,25; 20,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,31; 19,21</t>
+          <t>18,27; 19,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 18,23</t>
+          <t>17,23; 18,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,39; 18,81</t>
+          <t>17,29; 18,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 18,92</t>
+          <t>18,14; 18,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,21; 17,89</t>
+          <t>17,2; 17,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,5; 18,99</t>
+          <t>17,48; 19,02</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 20,49</t>
+          <t>19,41; 20,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,31; 19,11</t>
+          <t>18,26; 19,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,94; 19,4</t>
+          <t>17,97; 19,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,4; 20,7</t>
+          <t>19,49; 20,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,83</t>
+          <t>18,87; 19,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 20,12</t>
+          <t>18,65; 20,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 20,41</t>
+          <t>19,54; 20,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,28</t>
+          <t>18,7; 19,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,52; 19,6</t>
+          <t>18,55; 19,61</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 21,49</t>
+          <t>20,53; 21,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 21,15</t>
+          <t>20,28; 21,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,84; 22,31</t>
+          <t>19,82; 22,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 21,79</t>
+          <t>20,96; 21,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 21,31</t>
+          <t>20,35; 21,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,04; 21,5</t>
+          <t>19,97; 21,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,89; 21,52</t>
+          <t>20,87; 21,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,47; 21,14</t>
+          <t>20,48; 21,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 21,62</t>
+          <t>20,19; 21,68</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,18; 19,83</t>
+          <t>19,17; 19,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,04</t>
+          <t>18,5; 19,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,64</t>
+          <t>18,79; 20,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,45; 20,08</t>
+          <t>19,44; 20,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 19,26</t>
+          <t>18,7; 19,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,09; 19,96</t>
+          <t>19,07; 20,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,42; 19,89</t>
+          <t>19,44; 19,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,68; 19,09</t>
+          <t>18,68; 19,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 20,13</t>
+          <t>19,1; 20,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18,55</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17,51</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,86</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>19,13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>18,59</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,55</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,51</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,58</t>
+          <t>16,88</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,15</t>
+          <t>17,26</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,78; 21,14</t>
+          <t>17,2; 21,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 22,09</t>
+          <t>16,8; 18,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,22</t>
+          <t>16,29; 20,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 21,39</t>
+          <t>17,75; 21,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,69; 18,31</t>
+          <t>17,32; 21,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 20,56</t>
+          <t>15,15; 20,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 20,59</t>
+          <t>17,9; 20,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,28; 19,66</t>
+          <t>17,23; 19,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,68; 19,47</t>
+          <t>16,03; 20,24</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,71</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,65</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,98</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>18,16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17,35</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,28</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,71</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,65</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,99</t>
+          <t>17,92</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,11</t>
+          <t>17,96</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,7; 18,92</t>
+          <t>18,26; 19,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,92</t>
+          <t>17,21; 18,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,25; 20,25</t>
+          <t>17,34; 18,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,27; 19,21</t>
+          <t>17,66; 18,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 18,24</t>
+          <t>16,94; 17,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 18,82</t>
+          <t>17,14; 19,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 18,89</t>
+          <t>18,11; 18,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,2; 17,93</t>
+          <t>17,21; 17,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 19,02</t>
+          <t>17,45; 18,66</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,01</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,32</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19,37</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>19,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>18,65</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,32</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,35</t>
+          <t>18,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,03</t>
+          <t>19,05</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,41; 20,48</t>
+          <t>19,47; 20,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,26; 19,06</t>
+          <t>18,86; 19,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,97; 19,41</t>
+          <t>18,65; 20,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,49; 20,68</t>
+          <t>19,32; 20,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,87; 19,88</t>
+          <t>18,3; 19,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 20,2</t>
+          <t>17,96; 19,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 20,41</t>
+          <t>19,55; 20,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,34</t>
+          <t>18,66; 19,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,55; 19,61</t>
+          <t>18,53; 19,56</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21,36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,84</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20,8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>20,99</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>20,71</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20,84</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21,36</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,84</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,68</t>
+          <t>20,14</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,76</t>
+          <t>20,5</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,53; 21,49</t>
+          <t>20,98; 21,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 21,15</t>
+          <t>20,41; 21,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,82; 22,27</t>
+          <t>20,15; 21,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 21,8</t>
+          <t>20,52; 21,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,35; 21,36</t>
+          <t>20,28; 21,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,97; 21,5</t>
+          <t>19,48; 21,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 21,49</t>
+          <t>20,83; 21,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,48; 21,13</t>
+          <t>20,43; 21,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 21,68</t>
+          <t>20,0; 21,07</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>19,78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19,61</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>19,5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>18,77</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,47</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,49</t>
+          <t>19,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,48</t>
+          <t>19,35</t>
         </is>
       </c>
     </row>
@@ -1117,37 +1117,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 19,86</t>
+          <t>19,48; 20,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,5; 19,06</t>
+          <t>18,68; 19,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,79; 20,66</t>
+          <t>19,19; 20,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 20,08</t>
+          <t>19,19; 19,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,7; 19,31</t>
+          <t>18,52; 19,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 20,01</t>
+          <t>18,6; 19,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 19,87</t>
+          <t>19,42; 19,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>19,1; 20,12</t>
+          <t>19,02; 19,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>18,55</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17,51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,86</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,59</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>16,88</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,86</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18,06</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17,26</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>18.54539328879527</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>17.51468284005346</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.86347567374002</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>19.13318079299218</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>18.58877996991311</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>16.87843776474756</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>18.86486678814424</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>18.06096281286145</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>17.25715068436217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>17,2; 21,34</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16,8; 18,42</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16,29; 20,68</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17,75; 21,26</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17,32; 21,61</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,15; 20,71</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,9; 20,61</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17,23; 19,44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16,03; 20,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>17.19779645508791</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>16.80450201984456</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>16.28963354971767</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>17.75106131346412</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>17.32390348003705</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>15.14711815100329</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>17.89608301052521</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>17.22773431426494</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>16.02830564876802</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>21.34239403183002</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>18.41898768767472</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>20.6784787695436</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>21.26412209031882</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>21.60939587456905</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>20.70897961533841</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>20.61432364282092</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>19.44169546300629</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>20.24295841879587</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,71</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>17,65</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,98</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,35</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,92</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,45</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17,52</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17,96</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>18,26; 19,23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17,21; 18,26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17,34; 18,83</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17,66; 18,9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,94; 17,92</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>17,14; 19,08</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,11; 18,89</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17,21; 17,92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17,45; 18,66</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>18.71349612364969</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>17.65454090361457</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>17.9831895077111</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>18.15861913054536</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>17.34738346682893</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>17.91910637831625</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>18.45307109394649</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>17.5181945291132</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>17.95581510210841</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,01</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19,32</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,37</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19,92</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,65</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>18,63</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19,96</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>18.26131460319409</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>17.21320437320137</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>17.34213589157663</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>17.65787826361129</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>16.9362338598399</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>17.13992519970239</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>18.11447659904801</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>17.21001098085025</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>17.44584209445341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>19,47; 20,7</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18,86; 19,82</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>18,65; 20,18</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>19,32; 20,49</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>18,3; 19,05</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>17,96; 19,39</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>19,55; 20,41</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18,66; 19,3</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>18,53; 19,56</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>19.23284383560176</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>18.25741575347248</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>18.83265144903032</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>18.89945358248871</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>17.92051647663517</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>19.0776582180963</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>18.8885580751189</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>17.91623646848033</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>18.65971432521658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>21,36</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20,84</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20,8</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,99</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,71</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,14</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,18</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20,78</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20,5</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>20.0094757127144</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>19.32213936574264</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>19.3657653801262</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>19.91979383723794</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>18.64786023493076</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>18.62677243110544</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>19.96485743299987</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>18.98215839282471</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>19.04585126268808</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>20,98; 21,84</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>20,41; 21,32</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20,15; 21,66</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>20,52; 21,48</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>20,28; 21,14</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,48; 21,05</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20,83; 21,5</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20,43; 21,11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20,0; 21,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>19.46646000492004</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>18.85645294129432</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>18.6532977112454</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>19.31732441936205</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>18.30051935211253</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>17.95854244756795</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>19.54530337077314</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>18.66212284140301</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>18.52837646311162</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20.69650143853158</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>19.82149729146157</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>20.18171227559602</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>20.48974601152333</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>19.04762424265534</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>19.39073317231973</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>20.40742705143831</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>19.29725204167822</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>19.56048836247691</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>21.36271722805355</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>20.84290245667701</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>20.80476837557713</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>20.98833365108021</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>20.71420339561271</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>20.13500695213002</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>21.17821836538448</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>20.77999829689928</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>20.50397005725966</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>20.97814894930386</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>20.40740164341278</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>20.14840453762418</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>20.52031976711724</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>20.282823952381</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>19.47582694356294</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>20.83067242124252</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>20.42980914542197</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>20.00438055696801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>21.84035294585978</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.3245806828944</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>21.66163901735173</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>21.48051304441464</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>21.13795853266334</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>21.04704130359944</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>21.49736275676845</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>21.10911458516015</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>21.06645509472061</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>19,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18,98</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,61</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,77</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>19,03</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,64</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18,88</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>19,48; 20,09</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,31</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 20,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19,19; 19,89</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>18,52; 19,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,6; 19,61</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,42; 19,89</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18,68; 19,08</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19,02; 19,69</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>19.77734618549</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>18.97777263197639</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>19.60638206017093</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>19.50069028820386</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>18.77159943671817</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>19.02635636669282</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>19.64237760674442</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>18.87929111441086</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>19.34818702368086</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>19.48127154246051</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>18.68351430363325</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>19.18738829380854</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>19.18925687107792</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>18.52246053296223</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18.59656079178614</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>19.42259206053732</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>18.67598961102727</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>19.01897153474659</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>20.08600514812158</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>19.31294092105166</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>20.08517271000238</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>19.88627677988524</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>19.06876213998896</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>19.61027127031906</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>19.89025559794597</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>19.07831773694881</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>19.68628245385836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_Medido-Edad-trans_orig.xlsx
@@ -528,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 81,88%)</t>
+          <t>Índice de masa corporal (IMC) medio de los menores, recogido por medición (tasa de respuesta: 78,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
